--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run4/epoch_80/per_file_predictions_epoch_80.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run4/epoch_80/per_file_predictions_epoch_80.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.7785,0.1725,0.0255,0.0240</t>
-  </si>
-  <si>
-    <t>0.0591,0.0025,0.0006,0.9787</t>
-  </si>
-  <si>
-    <t>0.8760,0.0127,0.0011,0.1055</t>
-  </si>
-  <si>
-    <t>0.0293,0.0025,0.0037,0.9859</t>
-  </si>
-  <si>
-    <t>0.9937,0.0041,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9972,0.0015,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9937,0.0036,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.9931,0.0049,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9925,0.0055,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9949,0.0047,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0009,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0004,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.4086,0.0742,0.6202,0.0132</t>
-  </si>
-  <si>
-    <t>0.0247,0.0702,0.9410,0.0031</t>
-  </si>
-  <si>
-    <t>0.4833,0.0142,0.6930,0.0002</t>
-  </si>
-  <si>
-    <t>0.0303,0.0105,0.9640,0.0020</t>
-  </si>
-  <si>
-    <t>0.7201,0.0314,0.3277,0.0121</t>
-  </si>
-  <si>
-    <t>0.0065,0.9863,0.0078,0.0003</t>
-  </si>
-  <si>
-    <t>0.0091,0.9883,0.0015,0.0003</t>
-  </si>
-  <si>
-    <t>0.1096,0.8778,0.0023,0.0100</t>
-  </si>
-  <si>
-    <t>0.0132,0.9819,0.0011,0.0012</t>
-  </si>
-  <si>
-    <t>0.0019,0.9949,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.9528,0.0004,0.0739,0.0006</t>
-  </si>
-  <si>
-    <t>0.5386,0.0154,0.5598,0.0041</t>
-  </si>
-  <si>
-    <t>0.0035,0.0013,0.9947,0.0007</t>
-  </si>
-  <si>
-    <t>0.1476,0.0036,0.9039,0.0030</t>
-  </si>
-  <si>
-    <t>0.2980,0.0014,0.8493,0.0012</t>
-  </si>
-  <si>
-    <t>0.1815,0.0012,0.9153,0.0006</t>
-  </si>
-  <si>
-    <t>0.0071,0.0008,0.9904,0.0015</t>
-  </si>
-  <si>
-    <t>0.1940,0.8434,0.0100,0.0035</t>
-  </si>
-  <si>
-    <t>0.1791,0.6419,0.1592,0.0012</t>
-  </si>
-  <si>
-    <t>0.0063,0.0164,0.9777,0.0146</t>
-  </si>
-  <si>
-    <t>0.0144,0.8248,0.6122,0.0011</t>
-  </si>
-  <si>
-    <t>0.8776,0.0735,0.0345,0.0182</t>
-  </si>
-  <si>
-    <t>0.6501,0.0597,0.3173,0.0097</t>
-  </si>
-  <si>
-    <t>0.8324,0.1442,0.0332,0.0025</t>
-  </si>
-  <si>
-    <t>0.0079,0.9881,0.0229,0.0001</t>
-  </si>
-  <si>
-    <t>0.0065,0.9051,0.2926,0.0329</t>
-  </si>
-  <si>
-    <t>0.1442,0.0081,0.8327,0.0317</t>
-  </si>
-  <si>
-    <t>0.0254,0.2605,0.9290,0.0067</t>
-  </si>
-  <si>
-    <t>0.0767,0.0132,0.8711,0.0751</t>
-  </si>
-  <si>
-    <t>0.0740,0.1008,0.8615,0.0028</t>
-  </si>
-  <si>
-    <t>0.0700,0.8272,0.0772,0.0025</t>
-  </si>
-  <si>
-    <t>0.0096,0.0164,0.9709,0.0175</t>
-  </si>
-  <si>
-    <t>0.0110,0.9143,0.0071,0.6346</t>
-  </si>
-  <si>
-    <t>0.0024,0.9910,0.0022,0.0028</t>
-  </si>
-  <si>
-    <t>0.0019,0.9838,0.1582,0.0005</t>
-  </si>
-  <si>
-    <t>0.0022,0.9894,0.0342,0.0018</t>
-  </si>
-  <si>
-    <t>0.0011,0.0198,0.9844,0.0128</t>
-  </si>
-  <si>
-    <t>0.0018,0.2624,0.9898,0.0001</t>
-  </si>
-  <si>
-    <t>0.0099,0.0038,0.9552,0.0764</t>
-  </si>
-  <si>
-    <t>0.0931,0.0014,0.9525,0.0009</t>
-  </si>
-  <si>
-    <t>0.0100,0.0090,0.9848,0.0007</t>
-  </si>
-  <si>
-    <t>0.0357,0.0290,0.9368,0.0158</t>
-  </si>
-  <si>
-    <t>0.9601,0.0493,0.0019,0.0011</t>
-  </si>
-  <si>
-    <t>0.9675,0.0258,0.0054,0.0012</t>
-  </si>
-  <si>
-    <t>0.9207,0.1029,0.0111,0.0007</t>
-  </si>
-  <si>
-    <t>0.0004,0.0145,0.9974,0.0016</t>
-  </si>
-  <si>
-    <t>0.9902,0.0039,0.0022,0.0006</t>
-  </si>
-  <si>
-    <t>0.9930,0.0073,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9493,0.0486,0.0104,0.0015</t>
-  </si>
-  <si>
-    <t>0.0056,0.7480,0.9293,0.0017</t>
-  </si>
-  <si>
-    <t>0.0010,0.0063,0.9966,0.0008</t>
-  </si>
-  <si>
-    <t>0.0010,0.0011,0.9951,0.0062</t>
-  </si>
-  <si>
-    <t>0.0003,0.9816,0.9492,0.0001</t>
-  </si>
-  <si>
-    <t>0.0204,0.0042,0.9827,0.0005</t>
-  </si>
-  <si>
-    <t>0.0337,0.9287,0.0412,0.0009</t>
-  </si>
-  <si>
-    <t>0.0107,0.9779,0.0031,0.0013</t>
-  </si>
-  <si>
-    <t>0.9504,0.0264,0.0104,0.0033</t>
-  </si>
-  <si>
-    <t>0.6583,0.0981,0.3823,0.0063</t>
-  </si>
-  <si>
-    <t>0.0012,0.0440,0.9898,0.0015</t>
-  </si>
-  <si>
-    <t>0.0039,0.5299,0.9647,0.0003</t>
-  </si>
-  <si>
-    <t>0.0011,0.8385,0.9668,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.9922,0.2093,0.0002</t>
-  </si>
-  <si>
-    <t>0.0037,0.6368,0.9473,0.0009</t>
-  </si>
-  <si>
-    <t>0.0062,0.0012,0.0325,0.9850</t>
-  </si>
-  <si>
-    <t>0.0055,0.0024,0.0002,0.9979</t>
-  </si>
-  <si>
-    <t>0.0056,0.0314,0.0005,0.9939</t>
-  </si>
-  <si>
-    <t>0.0077,0.0038,0.0394,0.9779</t>
-  </si>
-  <si>
-    <t>0.0217,0.0025,0.0046,0.9866</t>
-  </si>
-  <si>
-    <t>0.0156,0.0041,0.0051,0.9884</t>
-  </si>
-  <si>
-    <t>0.0007,0.9838,0.6814,0.0001</t>
-  </si>
-  <si>
-    <t>0.0017,0.7835,0.9737,0.0001</t>
-  </si>
-  <si>
-    <t>0.0381,0.4951,0.8464,0.0078</t>
-  </si>
-  <si>
-    <t>0.0046,0.3227,0.9760,0.0004</t>
-  </si>
-  <si>
-    <t>0.0007,0.9534,0.7486,0.0000</t>
-  </si>
-  <si>
-    <t>0.0137,0.8000,0.7630,0.0010</t>
-  </si>
-  <si>
-    <t>0.9698,0.0367,0.0024,0.0006</t>
-  </si>
-  <si>
-    <t>0.9618,0.0640,0.0028,0.0003</t>
-  </si>
-  <si>
-    <t>0.9722,0.0379,0.0017,0.0007</t>
-  </si>
-  <si>
-    <t>0.9967,0.0009,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9840,0.0195,0.0013,0.0004</t>
-  </si>
-  <si>
-    <t>0.9962,0.0027,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9914,0.0057,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9739,0.0256,0.0045,0.0005</t>
-  </si>
-  <si>
-    <t>0.9958,0.0010,0.0004,0.0007</t>
-  </si>
-  <si>
-    <t>0.9947,0.0035,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9975,0.0013,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9932,0.0038,0.0012,0.0003</t>
-  </si>
-  <si>
-    <t>0.9984,0.0003,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9973,0.0009,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9934,0.0023,0.0008,0.0007</t>
-  </si>
-  <si>
-    <t>0.9973,0.0013,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0087,0.0018,0.9928,0.0003</t>
-  </si>
-  <si>
-    <t>0.2907,0.0130,0.8027,0.0007</t>
-  </si>
-  <si>
-    <t>0.8269,0.0070,0.0939,0.0316</t>
-  </si>
-  <si>
-    <t>0.5050,0.0035,0.7285,0.0005</t>
-  </si>
-  <si>
-    <t>0.0208,0.9755,0.0020,0.0006</t>
-  </si>
-  <si>
-    <t>0.0173,0.9738,0.0021,0.0017</t>
-  </si>
-  <si>
-    <t>0.0306,0.9637,0.0010,0.0016</t>
-  </si>
-  <si>
-    <t>0.3355,0.7094,0.0103,0.0056</t>
-  </si>
-  <si>
-    <t>0.0155,0.9738,0.0009,0.0026</t>
-  </si>
-  <si>
-    <t>0.0170,0.9720,0.0041,0.0015</t>
-  </si>
-  <si>
-    <t>0.6223,0.4981,0.0112,0.0011</t>
-  </si>
-  <si>
-    <t>0.4245,0.4353,0.1779,0.0166</t>
-  </si>
-  <si>
-    <t>0.4981,0.0019,0.7285,0.0019</t>
-  </si>
-  <si>
-    <t>0.7633,0.0565,0.1109,0.0505</t>
-  </si>
-  <si>
-    <t>0.5986,0.0749,0.3994,0.0148</t>
-  </si>
-  <si>
-    <t>0.5926,0.0358,0.2512,0.1838</t>
-  </si>
-  <si>
-    <t>0.0058,0.9870,0.0156,0.0008</t>
-  </si>
-  <si>
-    <t>0.0115,0.9786,0.0168,0.0030</t>
-  </si>
-  <si>
-    <t>0.0242,0.9248,0.1022,0.0041</t>
-  </si>
-  <si>
-    <t>0.0028,0.8922,0.8852,0.0010</t>
-  </si>
-  <si>
-    <t>0.0283,0.9781,0.0198,0.0001</t>
-  </si>
-  <si>
-    <t>0.7373,0.2770,0.0359,0.0028</t>
-  </si>
-  <si>
-    <t>0.3186,0.7520,0.0157,0.0021</t>
-  </si>
-  <si>
-    <t>0.9598,0.0241,0.0097,0.0037</t>
-  </si>
-  <si>
-    <t>0.9858,0.0125,0.0020,0.0004</t>
-  </si>
-  <si>
-    <t>0.9891,0.0056,0.0022,0.0008</t>
-  </si>
-  <si>
-    <t>0.9908,0.0020,0.0010,0.0018</t>
-  </si>
-  <si>
-    <t>0.9931,0.0006,0.0004,0.0025</t>
-  </si>
-  <si>
-    <t>0.9949,0.0039,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9943,0.0022,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.9863,0.0034,0.0103,0.0006</t>
-  </si>
-  <si>
-    <t>0.0076,0.1307,0.9671,0.0021</t>
-  </si>
-  <si>
-    <t>0.0175,0.4598,0.8925,0.0013</t>
-  </si>
-  <si>
-    <t>0.0745,0.0338,0.9173,0.0008</t>
-  </si>
-  <si>
-    <t>0.0198,0.0409,0.9600,0.0001</t>
-  </si>
-  <si>
-    <t>0.8851,0.0239,0.0621,0.0123</t>
-  </si>
-  <si>
-    <t>0.8787,0.0511,0.0561,0.0014</t>
-  </si>
-  <si>
-    <t>0.2864,0.0011,0.8096,0.0053</t>
-  </si>
-  <si>
-    <t>0.7490,0.0957,0.1481,0.0032</t>
-  </si>
-  <si>
-    <t>0.0758,0.0050,0.0037,0.9673</t>
-  </si>
-  <si>
-    <t>0.0032,0.0002,0.0002,0.9985</t>
-  </si>
-  <si>
-    <t>0.0021,0.0574,0.0006,0.9968</t>
-  </si>
-  <si>
-    <t>0.0131,0.0023,0.0004,0.9952</t>
-  </si>
-  <si>
-    <t>0.0017,0.8745,0.8943,0.0007</t>
-  </si>
-  <si>
-    <t>0.9768,0.0167,0.0038,0.0013</t>
-  </si>
-  <si>
-    <t>0.2255,0.7670,0.0290,0.0176</t>
-  </si>
-  <si>
-    <t>0.9947,0.0020,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.8181,0.2649,0.0083,0.0014</t>
-  </si>
-  <si>
-    <t>0.9595,0.0297,0.0057,0.0024</t>
-  </si>
-  <si>
-    <t>0.5442,0.0100,0.0104,0.5325</t>
-  </si>
-  <si>
-    <t>0.9817,0.0074,0.0017,0.0034</t>
-  </si>
-  <si>
-    <t>0.0005,0.0722,0.9935,0.0026</t>
-  </si>
-  <si>
-    <t>0.7539,0.0031,0.0019,0.3951</t>
-  </si>
-  <si>
-    <t>0.9708,0.0093,0.0046,0.0068</t>
-  </si>
-  <si>
-    <t>0.3647,0.6627,0.0135,0.0141</t>
-  </si>
-  <si>
-    <t>0.9510,0.0360,0.0085,0.0012</t>
-  </si>
-  <si>
-    <t>0.8964,0.1537,0.0036,0.0007</t>
-  </si>
-  <si>
-    <t>0.1298,0.7517,0.1513,0.0097</t>
-  </si>
-  <si>
-    <t>0.4249,0.6594,0.0062,0.0021</t>
-  </si>
-  <si>
-    <t>0.9371,0.0146,0.0327,0.0036</t>
-  </si>
-  <si>
-    <t>0.9838,0.0063,0.0012,0.0021</t>
-  </si>
-  <si>
-    <t>0.9925,0.0023,0.0008,0.0012</t>
-  </si>
-  <si>
-    <t>0.9932,0.0018,0.0009,0.0009</t>
-  </si>
-  <si>
-    <t>0.9890,0.0017,0.0005,0.0033</t>
-  </si>
-  <si>
-    <t>0.9902,0.0046,0.0012,0.0008</t>
-  </si>
-  <si>
-    <t>0.9931,0.0050,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9930,0.0045,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9945,0.0015,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.7924,0.2373,0.0062,0.0058</t>
-  </si>
-  <si>
-    <t>0.8685,0.1908,0.0070,0.0005</t>
-  </si>
-  <si>
-    <t>0.7042,0.3809,0.0128,0.0011</t>
-  </si>
-  <si>
-    <t>0.8933,0.0757,0.0412,0.0112</t>
-  </si>
-  <si>
-    <t>0.8668,0.2416,0.0028,0.0003</t>
-  </si>
-  <si>
-    <t>0.9484,0.0247,0.0066,0.0108</t>
-  </si>
-  <si>
-    <t>0.9629,0.0430,0.0032,0.0009</t>
-  </si>
-  <si>
-    <t>0.8990,0.1794,0.0025,0.0008</t>
-  </si>
-  <si>
-    <t>0.0012,0.0748,0.9943,0.0004</t>
-  </si>
-  <si>
-    <t>0.9675,0.0215,0.0075,0.0014</t>
-  </si>
-  <si>
-    <t>0.0092,0.0129,0.9872,0.0002</t>
-  </si>
-  <si>
-    <t>0.0337,0.1016,0.9321,0.0034</t>
-  </si>
-  <si>
-    <t>0.0855,0.0139,0.9326,0.0004</t>
-  </si>
-  <si>
-    <t>0.0049,0.0174,0.9837,0.0037</t>
-  </si>
-  <si>
-    <t>0.0263,0.0068,0.9740,0.0008</t>
-  </si>
-  <si>
-    <t>0.0013,0.0055,0.9967,0.0001</t>
-  </si>
-  <si>
-    <t>0.0099,0.0069,0.9822,0.0028</t>
-  </si>
-  <si>
-    <t>0.2994,0.0217,0.7583,0.0013</t>
-  </si>
-  <si>
-    <t>0.5024,0.0079,0.6801,0.0019</t>
-  </si>
-  <si>
-    <t>0.4864,0.1208,0.4338,0.0087</t>
-  </si>
-  <si>
-    <t>0.2411,0.2860,0.4005,0.0035</t>
-  </si>
-  <si>
-    <t>0.6276,0.0216,0.5203,0.0033</t>
-  </si>
-  <si>
-    <t>0.6024,0.0481,0.4258,0.0030</t>
-  </si>
-  <si>
-    <t>0.7080,0.0199,0.4219,0.0026</t>
-  </si>
-  <si>
-    <t>0.3085,0.0269,0.7843,0.0012</t>
-  </si>
-  <si>
-    <t>0.4225,0.7013,0.0095,0.0010</t>
-  </si>
-  <si>
-    <t>0.4849,0.6808,0.0013,0.0006</t>
-  </si>
-  <si>
-    <t>0.8901,0.2504,0.0012,0.0003</t>
-  </si>
-  <si>
-    <t>0.9537,0.0632,0.0059,0.0006</t>
-  </si>
-  <si>
-    <t>0.9609,0.0612,0.0029,0.0002</t>
-  </si>
-  <si>
-    <t>0.4517,0.2394,0.3315,0.0217</t>
-  </si>
-  <si>
-    <t>0.9102,0.0059,0.1023,0.0017</t>
-  </si>
-  <si>
-    <t>0.6150,0.0795,0.1697,0.1535</t>
-  </si>
-  <si>
-    <t>0.6094,0.0174,0.4645,0.0131</t>
-  </si>
-  <si>
-    <t>0.6554,0.0356,0.4106,0.0081</t>
-  </si>
-  <si>
-    <t>0.0080,0.0091,0.9727,0.0275</t>
-  </si>
-  <si>
-    <t>0.0084,0.0885,0.9641,0.0057</t>
-  </si>
-  <si>
-    <t>0.0186,0.3763,0.8893,0.0113</t>
-  </si>
-  <si>
-    <t>0.0433,0.0035,0.9597,0.0032</t>
-  </si>
-  <si>
-    <t>0.0539,0.3249,0.8530,0.0056</t>
-  </si>
-  <si>
-    <t>0.9967,0.0007,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9680,0.0226,0.0061,0.0023</t>
-  </si>
-  <si>
-    <t>0.9844,0.0091,0.0017,0.0017</t>
-  </si>
-  <si>
-    <t>0.9480,0.0888,0.0016,0.0008</t>
-  </si>
-  <si>
-    <t>0.9850,0.0134,0.0006,0.0009</t>
-  </si>
-  <si>
-    <t>0.9948,0.0013,0.0000,0.0006</t>
-  </si>
-  <si>
-    <t>0.9965,0.0010,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9883,0.0065,0.0027,0.0004</t>
-  </si>
-  <si>
-    <t>0.0726,0.0066,0.9542,0.0018</t>
-  </si>
-  <si>
-    <t>0.0626,0.7337,0.4147,0.0009</t>
-  </si>
-  <si>
-    <t>0.7544,0.0134,0.1900,0.0401</t>
-  </si>
-  <si>
-    <t>0.0184,0.0026,0.9858,0.0003</t>
-  </si>
-  <si>
-    <t>0.0072,0.0197,0.9806,0.0007</t>
-  </si>
-  <si>
-    <t>0.0557,0.0568,0.9026,0.0006</t>
-  </si>
-  <si>
-    <t>0.0075,0.0100,0.9839,0.0037</t>
-  </si>
-  <si>
-    <t>0.1400,0.0151,0.8894,0.0012</t>
-  </si>
-  <si>
-    <t>0.0052,0.0096,0.9845,0.0071</t>
-  </si>
-  <si>
-    <t>0.0127,0.0042,0.9835,0.0014</t>
-  </si>
-  <si>
-    <t>0.1740,0.0781,0.7851,0.0222</t>
-  </si>
-  <si>
-    <t>0.7265,0.0183,0.3577,0.0062</t>
-  </si>
-  <si>
-    <t>0.2848,0.0150,0.7757,0.0062</t>
-  </si>
-  <si>
-    <t>0.9466,0.0028,0.0504,0.0012</t>
-  </si>
-  <si>
-    <t>0.9931,0.0018,0.0005,0.0010</t>
-  </si>
-  <si>
-    <t>0.9932,0.0046,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9954,0.0019,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9420,0.0720,0.0068,0.0011</t>
-  </si>
-  <si>
-    <t>0.9962,0.0010,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.9729,0.0250,0.0040,0.0006</t>
-  </si>
-  <si>
-    <t>0.9841,0.0128,0.0026,0.0005</t>
-  </si>
-  <si>
-    <t>0.9904,0.0049,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>0.0086,0.0328,0.9499,0.0083</t>
-  </si>
-  <si>
-    <t>0.0063,0.1037,0.9674,0.0018</t>
-  </si>
-  <si>
-    <t>0.0104,0.0112,0.9824,0.0024</t>
-  </si>
-  <si>
-    <t>0.0841,0.0086,0.9383,0.0006</t>
-  </si>
-  <si>
-    <t>0.0117,0.0042,0.9856,0.0013</t>
-  </si>
-  <si>
-    <t>0.0687,0.0684,0.8215,0.1100</t>
-  </si>
-  <si>
-    <t>0.0812,0.1067,0.8404,0.0354</t>
-  </si>
-  <si>
-    <t>0.0337,0.0203,0.9179,0.0534</t>
-  </si>
-  <si>
-    <t>0.7584,0.0015,0.0029,0.3532</t>
-  </si>
-  <si>
-    <t>0.0677,0.0343,0.0010,0.9598</t>
-  </si>
-  <si>
-    <t>0.0777,0.0119,0.0029,0.9677</t>
-  </si>
-  <si>
-    <t>0.0175,0.0002,0.0007,0.9923</t>
-  </si>
-  <si>
-    <t>0.0098,0.0001,0.0000,0.9978</t>
-  </si>
-  <si>
-    <t>0.8983,0.0112,0.0235,0.0407</t>
+    <t>0.9486,0.0113,0.0112,0.0088</t>
+  </si>
+  <si>
+    <t>0.0109,0.0017,0.0005,0.9952</t>
+  </si>
+  <si>
+    <t>0.9309,0.0343,0.0019,0.0123</t>
+  </si>
+  <si>
+    <t>0.0260,0.0105,0.0053,0.9844</t>
+  </si>
+  <si>
+    <t>0.9984,0.0006,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9969,0.0019,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9910,0.0063,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.9954,0.0023,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9955,0.0028,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9942,0.0064,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9976,0.0007,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9930,0.0042,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.4195,0.2091,0.4281,0.0209</t>
+  </si>
+  <si>
+    <t>0.5468,0.0128,0.6253,0.0012</t>
+  </si>
+  <si>
+    <t>0.5344,0.0470,0.5233,0.0007</t>
+  </si>
+  <si>
+    <t>0.3258,0.0272,0.7370,0.0018</t>
+  </si>
+  <si>
+    <t>0.9487,0.0204,0.0243,0.0012</t>
+  </si>
+  <si>
+    <t>0.0008,0.9972,0.0026,0.0001</t>
+  </si>
+  <si>
+    <t>0.0024,0.9924,0.0118,0.0004</t>
+  </si>
+  <si>
+    <t>0.2799,0.7529,0.0204,0.0067</t>
+  </si>
+  <si>
+    <t>0.0593,0.9457,0.0031,0.0010</t>
+  </si>
+  <si>
+    <t>0.0030,0.9930,0.0024,0.0003</t>
+  </si>
+  <si>
+    <t>0.7033,0.0029,0.3598,0.0114</t>
+  </si>
+  <si>
+    <t>0.4638,0.0053,0.6352,0.0073</t>
+  </si>
+  <si>
+    <t>0.0856,0.0139,0.9276,0.0018</t>
+  </si>
+  <si>
+    <t>0.3099,0.1070,0.5952,0.0097</t>
+  </si>
+  <si>
+    <t>0.0581,0.0030,0.9497,0.0041</t>
+  </si>
+  <si>
+    <t>0.2662,0.0028,0.8286,0.0050</t>
+  </si>
+  <si>
+    <t>0.0224,0.0007,0.9833,0.0010</t>
+  </si>
+  <si>
+    <t>0.5220,0.5644,0.0156,0.0011</t>
+  </si>
+  <si>
+    <t>0.8208,0.1113,0.0876,0.0075</t>
+  </si>
+  <si>
+    <t>0.0050,0.0064,0.9853,0.0109</t>
+  </si>
+  <si>
+    <t>0.0146,0.9317,0.1710,0.0002</t>
+  </si>
+  <si>
+    <t>0.9583,0.0161,0.0029,0.0078</t>
+  </si>
+  <si>
+    <t>0.9203,0.0341,0.0333,0.0091</t>
+  </si>
+  <si>
+    <t>0.8463,0.2705,0.0027,0.0006</t>
+  </si>
+  <si>
+    <t>0.0231,0.9361,0.2913,0.0012</t>
+  </si>
+  <si>
+    <t>0.0123,0.4945,0.8607,0.0181</t>
+  </si>
+  <si>
+    <t>0.1783,0.0315,0.7725,0.0499</t>
+  </si>
+  <si>
+    <t>0.0940,0.0205,0.9270,0.0015</t>
+  </si>
+  <si>
+    <t>0.0579,0.0018,0.9153,0.0272</t>
+  </si>
+  <si>
+    <t>0.0137,0.3356,0.9600,0.0017</t>
+  </si>
+  <si>
+    <t>0.0504,0.7664,0.1812,0.0037</t>
+  </si>
+  <si>
+    <t>0.0208,0.0497,0.9341,0.0113</t>
+  </si>
+  <si>
+    <t>0.1084,0.5951,0.0078,0.6039</t>
+  </si>
+  <si>
+    <t>0.0180,0.9753,0.0019,0.0025</t>
+  </si>
+  <si>
+    <t>0.0054,0.9629,0.1965,0.0012</t>
+  </si>
+  <si>
+    <t>0.0059,0.9780,0.0650,0.0040</t>
+  </si>
+  <si>
+    <t>0.0011,0.1482,0.9770,0.0077</t>
+  </si>
+  <si>
+    <t>0.0061,0.3437,0.9784,0.0002</t>
+  </si>
+  <si>
+    <t>0.1824,0.0103,0.8144,0.0303</t>
+  </si>
+  <si>
+    <t>0.0054,0.0015,0.9929,0.0009</t>
+  </si>
+  <si>
+    <t>0.0059,0.0255,0.9861,0.0015</t>
+  </si>
+  <si>
+    <t>0.0070,0.0319,0.9748,0.0064</t>
+  </si>
+  <si>
+    <t>0.9592,0.0632,0.0025,0.0009</t>
+  </si>
+  <si>
+    <t>0.9827,0.0043,0.0057,0.0020</t>
+  </si>
+  <si>
+    <t>0.9767,0.0144,0.0022,0.0027</t>
+  </si>
+  <si>
+    <t>0.0012,0.0417,0.9935,0.0022</t>
+  </si>
+  <si>
+    <t>0.9830,0.0111,0.0029,0.0010</t>
+  </si>
+  <si>
+    <t>0.9957,0.0020,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9685,0.0291,0.0047,0.0011</t>
+  </si>
+  <si>
+    <t>0.0031,0.9071,0.8658,0.0021</t>
+  </si>
+  <si>
+    <t>0.0024,0.0373,0.9910,0.0013</t>
+  </si>
+  <si>
+    <t>0.0059,0.0088,0.9872,0.0036</t>
+  </si>
+  <si>
+    <t>0.0023,0.7646,0.9576,0.0003</t>
+  </si>
+  <si>
+    <t>0.0113,0.0018,0.9837,0.0025</t>
+  </si>
+  <si>
+    <t>0.0627,0.8083,0.1365,0.0008</t>
+  </si>
+  <si>
+    <t>0.0081,0.9869,0.0035,0.0001</t>
+  </si>
+  <si>
+    <t>0.8377,0.0243,0.2002,0.0060</t>
+  </si>
+  <si>
+    <t>0.5078,0.4403,0.1022,0.0036</t>
+  </si>
+  <si>
+    <t>0.0037,0.1319,0.9818,0.0009</t>
+  </si>
+  <si>
+    <t>0.0025,0.8682,0.8996,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.9757,0.9065,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9873,0.2465,0.0001</t>
+  </si>
+  <si>
+    <t>0.0021,0.9233,0.8296,0.0006</t>
+  </si>
+  <si>
+    <t>0.0030,0.0008,0.0239,0.9915</t>
+  </si>
+  <si>
+    <t>0.0060,0.0007,0.0002,0.9976</t>
+  </si>
+  <si>
+    <t>0.0037,0.0048,0.0001,0.9976</t>
+  </si>
+  <si>
+    <t>0.0111,0.0119,0.0150,0.9850</t>
+  </si>
+  <si>
+    <t>0.0076,0.0194,0.0070,0.9908</t>
+  </si>
+  <si>
+    <t>0.0307,0.0082,0.0006,0.9882</t>
+  </si>
+  <si>
+    <t>0.0004,0.9845,0.7003,0.0002</t>
+  </si>
+  <si>
+    <t>0.0262,0.4185,0.8803,0.0024</t>
+  </si>
+  <si>
+    <t>0.0150,0.3560,0.9238,0.0049</t>
+  </si>
+  <si>
+    <t>0.0028,0.4987,0.9717,0.0003</t>
+  </si>
+  <si>
+    <t>0.0012,0.8642,0.9447,0.0001</t>
+  </si>
+  <si>
+    <t>0.0031,0.9652,0.1370,0.0003</t>
+  </si>
+  <si>
+    <t>0.9918,0.0052,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.9640,0.0464,0.0028,0.0008</t>
+  </si>
+  <si>
+    <t>0.9560,0.0655,0.0022,0.0011</t>
+  </si>
+  <si>
+    <t>0.9849,0.0193,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9970,0.0004,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9960,0.0020,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9817,0.0267,0.0021,0.0002</t>
+  </si>
+  <si>
+    <t>0.9085,0.1254,0.0100,0.0007</t>
+  </si>
+  <si>
+    <t>0.9985,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9953,0.0032,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9968,0.0012,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9948,0.0032,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9923,0.0039,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9982,0.0008,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0355,0.0017,0.9699,0.0038</t>
+  </si>
+  <si>
+    <t>0.1089,0.0963,0.8329,0.0041</t>
+  </si>
+  <si>
+    <t>0.7998,0.0040,0.1547,0.0201</t>
+  </si>
+  <si>
+    <t>0.0801,0.0060,0.9477,0.0003</t>
+  </si>
+  <si>
+    <t>0.0111,0.9823,0.0012,0.0007</t>
+  </si>
+  <si>
+    <t>0.0084,0.9823,0.0023,0.0032</t>
+  </si>
+  <si>
+    <t>0.0576,0.9402,0.0035,0.0024</t>
+  </si>
+  <si>
+    <t>0.0963,0.9080,0.0121,0.0022</t>
+  </si>
+  <si>
+    <t>0.0236,0.9643,0.0020,0.0037</t>
+  </si>
+  <si>
+    <t>0.0198,0.9672,0.0064,0.0012</t>
+  </si>
+  <si>
+    <t>0.8544,0.2212,0.0079,0.0009</t>
+  </si>
+  <si>
+    <t>0.7960,0.0502,0.1265,0.0177</t>
+  </si>
+  <si>
+    <t>0.3446,0.0057,0.8145,0.0013</t>
+  </si>
+  <si>
+    <t>0.8763,0.0281,0.0319,0.0126</t>
+  </si>
+  <si>
+    <t>0.5285,0.0642,0.4829,0.0120</t>
+  </si>
+  <si>
+    <t>0.3383,0.1927,0.0646,0.6486</t>
+  </si>
+  <si>
+    <t>0.0078,0.9867,0.0127,0.0003</t>
+  </si>
+  <si>
+    <t>0.0158,0.9648,0.0328,0.0077</t>
+  </si>
+  <si>
+    <t>0.0261,0.9277,0.0493,0.0615</t>
+  </si>
+  <si>
+    <t>0.0024,0.6716,0.9409,0.0026</t>
+  </si>
+  <si>
+    <t>0.0295,0.9724,0.0194,0.0002</t>
+  </si>
+  <si>
+    <t>0.2977,0.4472,0.3033,0.0021</t>
+  </si>
+  <si>
+    <t>0.3445,0.7366,0.0187,0.0010</t>
+  </si>
+  <si>
+    <t>0.9842,0.0111,0.0027,0.0009</t>
+  </si>
+  <si>
+    <t>0.9867,0.0058,0.0012,0.0016</t>
+  </si>
+  <si>
+    <t>0.9900,0.0025,0.0010,0.0021</t>
+  </si>
+  <si>
+    <t>0.9763,0.0061,0.0058,0.0053</t>
+  </si>
+  <si>
+    <t>0.9912,0.0023,0.0007,0.0016</t>
+  </si>
+  <si>
+    <t>0.9825,0.0037,0.0095,0.0014</t>
+  </si>
+  <si>
+    <t>0.9869,0.0030,0.0031,0.0036</t>
+  </si>
+  <si>
+    <t>0.9731,0.0059,0.0147,0.0033</t>
+  </si>
+  <si>
+    <t>0.0017,0.8060,0.9570,0.0004</t>
+  </si>
+  <si>
+    <t>0.0020,0.9087,0.7630,0.0001</t>
+  </si>
+  <si>
+    <t>0.0154,0.2121,0.8989,0.0003</t>
+  </si>
+  <si>
+    <t>0.0512,0.1345,0.8371,0.0019</t>
+  </si>
+  <si>
+    <t>0.8561,0.0708,0.0381,0.0143</t>
+  </si>
+  <si>
+    <t>0.7788,0.0131,0.3597,0.0027</t>
+  </si>
+  <si>
+    <t>0.5816,0.0023,0.7123,0.0009</t>
+  </si>
+  <si>
+    <t>0.8955,0.0075,0.1123,0.0035</t>
+  </si>
+  <si>
+    <t>0.0489,0.0138,0.0013,0.9788</t>
+  </si>
+  <si>
+    <t>0.0013,0.0002,0.0032,0.9975</t>
+  </si>
+  <si>
+    <t>0.0014,0.0189,0.0002,0.9984</t>
+  </si>
+  <si>
+    <t>0.0181,0.0061,0.0025,0.9900</t>
+  </si>
+  <si>
+    <t>0.0086,0.7502,0.6649,0.0044</t>
+  </si>
+  <si>
+    <t>0.9488,0.0520,0.0060,0.0024</t>
+  </si>
+  <si>
+    <t>0.0871,0.9116,0.0054,0.0066</t>
+  </si>
+  <si>
+    <t>0.9815,0.0118,0.0023,0.0017</t>
+  </si>
+  <si>
+    <t>0.5212,0.5643,0.0197,0.0035</t>
+  </si>
+  <si>
+    <t>0.9821,0.0046,0.0037,0.0038</t>
+  </si>
+  <si>
+    <t>0.9013,0.0030,0.0016,0.1147</t>
+  </si>
+  <si>
+    <t>0.9793,0.0108,0.0031,0.0019</t>
+  </si>
+  <si>
+    <t>0.0001,0.1804,0.9946,0.0012</t>
+  </si>
+  <si>
+    <t>0.9199,0.0009,0.0008,0.1099</t>
+  </si>
+  <si>
+    <t>0.9108,0.0423,0.0438,0.0086</t>
+  </si>
+  <si>
+    <t>0.3723,0.6778,0.0040,0.0118</t>
+  </si>
+  <si>
+    <t>0.9414,0.0431,0.0081,0.0015</t>
+  </si>
+  <si>
+    <t>0.9342,0.0552,0.0069,0.0014</t>
+  </si>
+  <si>
+    <t>0.1444,0.8244,0.0383,0.0314</t>
+  </si>
+  <si>
+    <t>0.7051,0.2110,0.1147,0.0085</t>
+  </si>
+  <si>
+    <t>0.8900,0.1525,0.0056,0.0009</t>
+  </si>
+  <si>
+    <t>0.9869,0.0112,0.0011,0.0006</t>
+  </si>
+  <si>
+    <t>0.9894,0.0050,0.0008,0.0013</t>
+  </si>
+  <si>
+    <t>0.9958,0.0017,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9949,0.0011,0.0003,0.0012</t>
+  </si>
+  <si>
+    <t>0.9603,0.0240,0.0074,0.0038</t>
+  </si>
+  <si>
+    <t>0.9888,0.0090,0.0012,0.0003</t>
+  </si>
+  <si>
+    <t>0.9941,0.0020,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9909,0.0044,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.8960,0.1292,0.0017,0.0029</t>
+  </si>
+  <si>
+    <t>0.7042,0.3335,0.0156,0.0003</t>
+  </si>
+  <si>
+    <t>0.8802,0.2091,0.0030,0.0005</t>
+  </si>
+  <si>
+    <t>0.3288,0.5981,0.1915,0.0046</t>
+  </si>
+  <si>
+    <t>0.9408,0.0738,0.0069,0.0009</t>
+  </si>
+  <si>
+    <t>0.9248,0.0803,0.0107,0.0033</t>
+  </si>
+  <si>
+    <t>0.9809,0.0151,0.0044,0.0006</t>
+  </si>
+  <si>
+    <t>0.9364,0.0563,0.0113,0.0039</t>
+  </si>
+  <si>
+    <t>0.0008,0.2820,0.9900,0.0003</t>
+  </si>
+  <si>
+    <t>0.8616,0.1743,0.0212,0.0050</t>
+  </si>
+  <si>
+    <t>0.0130,0.0031,0.9849,0.0012</t>
+  </si>
+  <si>
+    <t>0.0068,0.1315,0.9656,0.0017</t>
+  </si>
+  <si>
+    <t>0.0791,0.0119,0.9354,0.0046</t>
+  </si>
+  <si>
+    <t>0.0243,0.0274,0.9794,0.0002</t>
+  </si>
+  <si>
+    <t>0.0247,0.0076,0.9745,0.0009</t>
+  </si>
+  <si>
+    <t>0.0145,0.0034,0.9876,0.0004</t>
+  </si>
+  <si>
+    <t>0.0347,0.0109,0.9623,0.0020</t>
+  </si>
+  <si>
+    <t>0.3428,0.0247,0.7564,0.0021</t>
+  </si>
+  <si>
+    <t>0.0984,0.0138,0.9245,0.0015</t>
+  </si>
+  <si>
+    <t>0.6986,0.1278,0.0839,0.0742</t>
+  </si>
+  <si>
+    <t>0.3590,0.0584,0.5866,0.0019</t>
+  </si>
+  <si>
+    <t>0.0935,0.6981,0.2643,0.0104</t>
+  </si>
+  <si>
+    <t>0.7823,0.0925,0.1148,0.0020</t>
+  </si>
+  <si>
+    <t>0.8382,0.0205,0.1762,0.0079</t>
+  </si>
+  <si>
+    <t>0.2688,0.1451,0.6344,0.0234</t>
+  </si>
+  <si>
+    <t>0.5817,0.5537,0.0072,0.0005</t>
+  </si>
+  <si>
+    <t>0.8371,0.3215,0.0040,0.0004</t>
+  </si>
+  <si>
+    <t>0.9562,0.0739,0.0024,0.0003</t>
+  </si>
+  <si>
+    <t>0.9613,0.0606,0.0036,0.0003</t>
+  </si>
+  <si>
+    <t>0.6243,0.5274,0.0049,0.0009</t>
+  </si>
+  <si>
+    <t>0.3508,0.5543,0.0473,0.0077</t>
+  </si>
+  <si>
+    <t>0.7873,0.0489,0.1811,0.0127</t>
+  </si>
+  <si>
+    <t>0.7704,0.0526,0.0599,0.0635</t>
+  </si>
+  <si>
+    <t>0.1677,0.1406,0.6936,0.0037</t>
+  </si>
+  <si>
+    <t>0.8028,0.0949,0.0978,0.0057</t>
+  </si>
+  <si>
+    <t>0.1073,0.0161,0.9014,0.0090</t>
+  </si>
+  <si>
+    <t>0.0938,0.0783,0.8326,0.0058</t>
+  </si>
+  <si>
+    <t>0.1024,0.0416,0.9128,0.0012</t>
+  </si>
+  <si>
+    <t>0.0589,0.0104,0.9261,0.0130</t>
+  </si>
+  <si>
+    <t>0.0534,0.2260,0.7620,0.0188</t>
+  </si>
+  <si>
+    <t>0.9956,0.0009,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9917,0.0055,0.0017,0.0003</t>
+  </si>
+  <si>
+    <t>0.9878,0.0094,0.0022,0.0006</t>
+  </si>
+  <si>
+    <t>0.9846,0.0191,0.0017,0.0002</t>
+  </si>
+  <si>
+    <t>0.9772,0.0312,0.0016,0.0004</t>
+  </si>
+  <si>
+    <t>0.9947,0.0046,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9969,0.0011,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9962,0.0026,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0368,0.0090,0.9593,0.0036</t>
+  </si>
+  <si>
+    <t>0.0812,0.0730,0.8911,0.0060</t>
+  </si>
+  <si>
+    <t>0.7470,0.0028,0.0619,0.1115</t>
+  </si>
+  <si>
+    <t>0.0653,0.0018,0.9732,0.0002</t>
+  </si>
+  <si>
+    <t>0.0087,0.0271,0.9651,0.0029</t>
+  </si>
+  <si>
+    <t>0.0800,0.1138,0.8534,0.0003</t>
+  </si>
+  <si>
+    <t>0.0019,0.0029,0.9968,0.0002</t>
+  </si>
+  <si>
+    <t>0.0178,0.0294,0.9586,0.0023</t>
+  </si>
+  <si>
+    <t>0.0029,0.0029,0.9919,0.0028</t>
+  </si>
+  <si>
+    <t>0.0210,0.0096,0.9702,0.0019</t>
+  </si>
+  <si>
+    <t>0.0777,0.2346,0.7533,0.0208</t>
+  </si>
+  <si>
+    <t>0.8870,0.0041,0.1615,0.0017</t>
+  </si>
+  <si>
+    <t>0.6297,0.0080,0.5279,0.0033</t>
+  </si>
+  <si>
+    <t>0.9122,0.0143,0.0623,0.0035</t>
+  </si>
+  <si>
+    <t>0.9931,0.0052,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9909,0.0063,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9941,0.0035,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9497,0.0786,0.0036,0.0005</t>
+  </si>
+  <si>
+    <t>0.9969,0.0005,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9774,0.0337,0.0016,0.0002</t>
+  </si>
+  <si>
+    <t>0.9899,0.0077,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9927,0.0031,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.0273,0.1733,0.8985,0.0017</t>
+  </si>
+  <si>
+    <t>0.0023,0.0200,0.9893,0.0030</t>
+  </si>
+  <si>
+    <t>0.0151,0.0314,0.9616,0.0022</t>
+  </si>
+  <si>
+    <t>0.0522,0.0435,0.9032,0.0011</t>
+  </si>
+  <si>
+    <t>0.0042,0.0031,0.9897,0.0030</t>
+  </si>
+  <si>
+    <t>0.3525,0.3124,0.3497,0.1759</t>
+  </si>
+  <si>
+    <t>0.2300,0.0181,0.8372,0.0036</t>
+  </si>
+  <si>
+    <t>0.0480,0.0325,0.8983,0.0465</t>
+  </si>
+  <si>
+    <t>0.8299,0.0021,0.0092,0.1812</t>
+  </si>
+  <si>
+    <t>0.0793,0.0078,0.0006,0.9674</t>
+  </si>
+  <si>
+    <t>0.0310,0.0042,0.0080,0.9794</t>
+  </si>
+  <si>
+    <t>0.0045,0.0000,0.0001,0.9986</t>
+  </si>
+  <si>
+    <t>0.0096,0.0028,0.0002,0.9961</t>
+  </si>
+  <si>
+    <t>0.9283,0.0064,0.0536,0.0073</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1996,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,10 +2133,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,10 +2147,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,10 +2161,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2234,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2267,7 +2276,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2281,7 +2290,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,10 +2371,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,10 +2385,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,10 +2413,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,7 +2444,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,7 +2458,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,10 +2483,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2920,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2934,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2990,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +3004,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,10 +3113,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3130,7 @@
         <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3144,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3158,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,10 +3169,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3438,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3541,7 +3550,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3564,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3583,7 +3592,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3597,7 +3606,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,10 +3617,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3676,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,10 +3701,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3718,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,10 +3841,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,10 +3855,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3872,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3914,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,10 +3925,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4012,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,7 +4040,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,10 +4065,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,10 +4093,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,7 +4166,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4199,7 +4208,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,10 +4219,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,7 +4362,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,7 +4376,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4390,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,10 +4401,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4600,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4619,7 +4628,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4639,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4653,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4661,7 +4670,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4684,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,7 +4698,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,10 +4709,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,10 +4723,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,10 +4765,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,10 +4779,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4810,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,10 +4821,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4908,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5045,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5174,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,10 +5199,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,10 +5409,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5440,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5454,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5524,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
